--- a/AAII_Financials/Yearly/DUO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUO_YR_FIN.xlsx
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>2700</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1267,13 +1267,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="E21" s="3">
         <v>3100</v>
       </c>
       <c r="F21" s="3">
-        <v>-11000</v>
+        <v>-10900</v>
       </c>
       <c r="G21" s="3">
         <v>-21200</v>
